--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -16749,16 +16749,16 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O100" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.2828065101030238</v>
+        <v>0.2864793219225436</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17589,16 +17589,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O105" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19465,16 +19465,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O117" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.2424055800883061</v>
+        <v>0.2534240155468655</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22429,16 +22429,16 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9104</v>
+        <v>9113</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -20953,16 +20953,16 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O123" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0.2607696391859051</v>
+        <v>0.2644424510054249</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -23917,16 +23917,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24143,6 +24143,154 @@
       <c r="BC142" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>148</v>
+      </c>
+      <c r="O143" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.1208876443197334</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24179,7 +24327,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -24262,7 +24410,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -24272,7 +24420,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -24324,7 +24472,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9127</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>11</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>97</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>19</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.3379737424641861</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>17</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.03294548870446478</v>
       </c>
@@ -2395,7 +2380,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2542,9 +2527,6 @@
       <c r="O12" t="n">
         <v>74</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.6915211516929677</v>
       </c>
@@ -4418,9 +4400,6 @@
       <c r="O24" t="n">
         <v>23</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4811,9 +4790,6 @@
       <c r="O26" t="n">
         <v>86</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.954728336492448</v>
       </c>
@@ -4959,9 +4935,6 @@
       <c r="O27" t="n">
         <v>16</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.284609467338262</v>
       </c>
@@ -5355,9 +5328,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -5503,9 +5473,6 @@
       <c r="O30" t="n">
         <v>22</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.04263533832342501</v>
       </c>
@@ -5900,7 +5867,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6047,9 +6014,6 @@
       <c r="O33" t="n">
         <v>51</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.4765889018424507</v>
       </c>
@@ -7775,9 +7739,6 @@
       <c r="O44" t="n">
         <v>13</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8168,9 +8129,6 @@
       <c r="O46" t="n">
         <v>107</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>1.187859674473162</v>
       </c>
@@ -8316,9 +8274,6 @@
       <c r="O47" t="n">
         <v>30</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.5336427512592412</v>
       </c>
@@ -8712,9 +8667,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8860,9 +8812,6 @@
       <c r="O50" t="n">
         <v>20</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.03875939847584092</v>
       </c>
@@ -9257,7 +9206,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -9404,9 +9353,6 @@
       <c r="O53" t="n">
         <v>75</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.700866032121251</v>
       </c>
@@ -10984,9 +10930,6 @@
       <c r="O63" t="n">
         <v>79</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.2901521337420634</v>
       </c>
@@ -11132,9 +11075,6 @@
       <c r="O64" t="n">
         <v>11</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11525,9 +11465,6 @@
       <c r="O66" t="n">
         <v>108</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>1.198961166757958</v>
       </c>
@@ -11673,9 +11610,6 @@
       <c r="O67" t="n">
         <v>14</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.2490332839209793</v>
       </c>
@@ -12069,9 +12003,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12217,9 +12148,6 @@
       <c r="O70" t="n">
         <v>21</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.04069736839963296</v>
       </c>
@@ -12365,9 +12293,6 @@
       <c r="O71" t="n">
         <v>87</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>1.645396605830491</v>
       </c>
@@ -12614,7 +12539,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -12761,9 +12686,6 @@
       <c r="O73" t="n">
         <v>64</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.5980723474101342</v>
       </c>
@@ -14341,9 +14263,6 @@
       <c r="O83" t="n">
         <v>73</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.2681152628249447</v>
       </c>
@@ -14489,9 +14408,6 @@
       <c r="O84" t="n">
         <v>13</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14882,9 +14798,6 @@
       <c r="O86" t="n">
         <v>132</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>1.46539698159306</v>
       </c>
@@ -15030,9 +14943,6 @@
       <c r="O87" t="n">
         <v>21</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.3735499258814688</v>
       </c>
@@ -15426,9 +15336,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15574,9 +15481,6 @@
       <c r="O90" t="n">
         <v>39</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.07558082702788979</v>
       </c>
@@ -15722,9 +15626,6 @@
       <c r="O91" t="n">
         <v>78</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>1.475183163848027</v>
       </c>
@@ -15971,7 +15872,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -16118,9 +16019,6 @@
       <c r="O93" t="n">
         <v>46</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.4298644997010339</v>
       </c>
@@ -17846,9 +17744,6 @@
       <c r="O104" t="n">
         <v>117</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.03352094615340181</v>
       </c>
@@ -17994,9 +17889,6 @@
       <c r="O105" t="n">
         <v>78</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.2864793219225436</v>
       </c>
@@ -18142,9 +18034,6 @@
       <c r="O106" t="n">
         <v>154</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>1.70962981185857</v>
       </c>
@@ -18290,9 +18179,6 @@
       <c r="O107" t="n">
         <v>24</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.426914201007393</v>
       </c>
@@ -18686,9 +18572,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -18834,9 +18717,6 @@
       <c r="O110" t="n">
         <v>124</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2403082705502137</v>
       </c>
@@ -18982,9 +18862,6 @@
       <c r="O111" t="n">
         <v>53</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>1.002368047230069</v>
       </c>
@@ -19231,7 +19108,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -19378,9 +19255,6 @@
       <c r="O113" t="n">
         <v>63</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.5887274669818509</v>
       </c>
@@ -19774,9 +19648,6 @@
       <c r="O115" t="n">
         <v>42</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.03430595311776218</v>
       </c>
@@ -19922,9 +19793,6 @@
       <c r="O116" t="n">
         <v>207</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.05930628934832628</v>
       </c>
@@ -20070,9 +19938,6 @@
       <c r="O117" t="n">
         <v>82</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.06697828942039284</v>
       </c>
@@ -20218,9 +20083,6 @@
       <c r="O118" t="n">
         <v>211</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.06045230460143403</v>
       </c>
@@ -20366,9 +20228,6 @@
       <c r="O119" t="n">
         <v>97</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.07923041553387933</v>
       </c>
@@ -20514,9 +20373,6 @@
       <c r="O120" t="n">
         <v>170</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.04870564825707954</v>
       </c>
@@ -20662,9 +20518,6 @@
       <c r="O121" t="n">
         <v>126</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.1029178593532865</v>
       </c>
@@ -20810,9 +20663,6 @@
       <c r="O122" t="n">
         <v>170</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.04870564825707954</v>
       </c>
@@ -20958,9 +20808,6 @@
       <c r="O123" t="n">
         <v>72</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.2644424510054249</v>
       </c>
@@ -21106,9 +20953,6 @@
       <c r="O124" t="n">
         <v>34</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.6047951180938068</v>
       </c>
@@ -21497,16 +21341,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O126" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2713157893308865</v>
+        <v>0.2732537592546785</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -21650,9 +21491,6 @@
       <c r="O127" t="n">
         <v>125</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>1.168110053535418</v>
       </c>
@@ -22046,9 +21884,6 @@
       <c r="O129" t="n">
         <v>123</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.1004674341305892</v>
       </c>
@@ -22194,9 +22029,6 @@
       <c r="O130" t="n">
         <v>168</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.04813264063052567</v>
       </c>
@@ -22342,9 +22174,6 @@
       <c r="O131" t="n">
         <v>99</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.08086403234901086</v>
       </c>
@@ -22490,9 +22319,6 @@
       <c r="O132" t="n">
         <v>215</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.06159831985454178</v>
       </c>
@@ -22638,9 +22464,6 @@
       <c r="O133" t="n">
         <v>83</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0677950978279586</v>
       </c>
@@ -22786,9 +22609,6 @@
       <c r="O134" t="n">
         <v>287</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.08222659441048136</v>
       </c>
@@ -22934,9 +22754,6 @@
       <c r="O135" t="n">
         <v>126</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.1029178593532865</v>
       </c>
@@ -23082,9 +22899,6 @@
       <c r="O136" t="n">
         <v>297</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.08509163254325074</v>
       </c>
@@ -23230,9 +23044,6 @@
       <c r="O137" t="n">
         <v>108</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.08821530801710276</v>
       </c>
@@ -23378,9 +23189,6 @@
       <c r="O138" t="n">
         <v>5</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.01836405909759895</v>
       </c>
@@ -23521,16 +23329,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R139" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23683,10 +23488,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -23922,9 +23727,6 @@
       <c r="O141" t="n">
         <v>9</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.01744172931412841</v>
       </c>
@@ -24070,9 +23872,6 @@
       <c r="O142" t="n">
         <v>288</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.0825130982237583</v>
       </c>
@@ -24218,9 +24017,6 @@
       <c r="O143" t="n">
         <v>148</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1208876443197334</v>
       </c>
@@ -24291,6 +24087,151 @@
       <c r="BC143" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>310</v>
+      </c>
+      <c r="O144" t="n">
+        <v>310</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.08881618211585095</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24327,7 +24268,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -24410,7 +24351,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -24420,7 +24361,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -24472,7 +24413,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9278</v>
+        <v>9592</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -4785,13 +4785,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O26" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R26" t="n">
-        <v>0.954728336492448</v>
+        <v>0.9658298287772439</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -8124,13 +8124,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O46" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R46" t="n">
-        <v>1.187859674473162</v>
+        <v>1.210062659042754</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -11460,13 +11460,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O66" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R66" t="n">
-        <v>1.198961166757958</v>
+        <v>1.232265643612346</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -14793,13 +14793,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O86" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R86" t="n">
-        <v>1.46539698159306</v>
+        <v>1.476498473877856</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -18029,13 +18029,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="O106" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="R106" t="n">
-        <v>1.70962981185857</v>
+        <v>1.820644734706529</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -20909,12 +20909,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20948,95 +20948,81 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="O124" t="n">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="R124" t="n">
-        <v>0.6047951180938068</v>
+        <v>2.697662625205405</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21063,7 +21049,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -21112,98 +21098,23 @@
       <c r="O125" t="n">
         <v>34</v>
       </c>
+      <c r="R125" t="n">
+        <v>0.6047951180938068</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -21297,17 +21208,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21341,81 +21252,170 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="O126" t="n">
-        <v>141</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.2732537592546785</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21447,12 +21447,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21486,95 +21486,81 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="O127" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="R127" t="n">
-        <v>1.168110053535418</v>
+        <v>0.2732537592546785</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21587,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21650,98 +21636,23 @@
       <c r="O128" t="n">
         <v>125</v>
       </c>
+      <c r="R128" t="n">
+        <v>1.168110053535418</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -21835,17 +21746,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21870,7 +21781,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21879,81 +21790,170 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O129" t="n">
-        <v>123</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.1004674341305892</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21985,12 +21985,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22024,13 +22024,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="O130" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="R130" t="n">
-        <v>0.04813264063052567</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22063,42 +22063,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22130,12 +22130,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22169,13 +22169,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="O131" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="R131" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22208,42 +22208,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22275,12 +22275,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>215</v>
+        <v>99</v>
       </c>
       <c r="O132" t="n">
-        <v>215</v>
+        <v>99</v>
       </c>
       <c r="R132" t="n">
-        <v>0.06159831985454178</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22353,42 +22353,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22420,12 +22420,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22459,13 +22459,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="O133" t="n">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22498,42 +22498,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22565,12 +22565,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22604,13 +22604,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="O134" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="R134" t="n">
-        <v>0.08222659441048136</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22643,42 +22643,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22710,12 +22710,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -22749,13 +22749,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="O135" t="n">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="R135" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22788,42 +22788,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22855,12 +22855,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22894,13 +22894,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="O136" t="n">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="R136" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -22933,42 +22933,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23000,12 +23000,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23039,13 +23039,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>108</v>
+        <v>297</v>
       </c>
       <c r="O137" t="n">
-        <v>108</v>
+        <v>297</v>
       </c>
       <c r="R137" t="n">
-        <v>0.08821530801710276</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23078,42 +23078,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23145,12 +23145,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23175,22 +23175,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="O138" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="R138" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.08821530801710276</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23223,42 +23223,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23290,12 +23290,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23329,95 +23329,81 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R139" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23444,7 +23430,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -23488,103 +23474,28 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O140" t="n">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.2490332839209793</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -23678,17 +23589,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23722,81 +23633,170 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O141" t="n">
-        <v>9</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.01744172931412841</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23828,12 +23828,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23867,13 +23867,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>288</v>
+        <v>9</v>
       </c>
       <c r="O142" t="n">
-        <v>288</v>
+        <v>9</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0825130982237583</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -23906,42 +23906,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23973,12 +23973,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24012,13 +24012,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="O143" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24051,42 +24051,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24118,12 +24118,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24157,13 +24157,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="O144" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="R144" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24196,40 +24196,185 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>310</v>
+      </c>
+      <c r="O145" t="n">
+        <v>310</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.08881618211585095</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW144" t="inlineStr">
+      <c r="AW145" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
+      <c r="AX145" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY144" t="inlineStr">
+      <c r="AY145" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
+      <c r="AZ145" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA144" t="inlineStr">
+      <c r="BA145" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB144" t="inlineStr">
+      <c r="BB145" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC144" t="inlineStr">
+      <c r="BC145" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24351,7 +24496,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -24361,7 +24506,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -24413,7 +24558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9592</v>
+        <v>9856</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -18712,13 +18712,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O110" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R110" t="n">
-        <v>0.2403082705502137</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O127" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R127" t="n">
-        <v>0.2732537592546785</v>
+        <v>0.2751917291784705</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -23867,13 +23867,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O142" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R142" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9856</v>
+        <v>9860</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -17884,13 +17884,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O105" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R105" t="n">
-        <v>0.2864793219225436</v>
+        <v>0.2901521337420634</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20803,13 +20803,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O123" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R123" t="n">
-        <v>0.2644424510054249</v>
+        <v>0.2607696391859051</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -23329,13 +23329,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R139" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.02203687091711874</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23474,13 +23474,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O140" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R140" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23633,10 +23633,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O141" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9860</v>
+        <v>9863</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -17990,12 +17990,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18029,81 +18029,92 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="O106" t="n">
-        <v>164</v>
-      </c>
-      <c r="R106" t="n">
-        <v>1.820644734706529</v>
+        <v>25</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18130,17 +18141,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18174,22 +18185,39 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O107" t="n">
-        <v>24</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0.426914201007393</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Verotoxin Producing E. Coli Including HUS</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -18197,6 +18225,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary culture-confirmed verotoxin-producing Escherichia coli infection notifications. Although the source title mentions HUS, probable HUS-only, toxin-only and NAAT-only cases are excluded from July 2026 IDTO totals.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18209,12 +18295,12 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -18222,47 +18308,47 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18289,17 +18375,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18333,170 +18419,81 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="O108" t="n">
-        <v>24</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1.820644734706529</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -18528,12 +18525,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18567,81 +18564,95 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="R109" t="n">
-        <v>0.02710540560393419</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18668,17 +18679,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18712,81 +18723,170 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="O110" t="n">
-        <v>125</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.2422462404740058</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18818,12 +18918,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18857,95 +18957,81 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>1.002368047230069</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18972,17 +19058,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19016,170 +19102,81 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="O112" t="n">
-        <v>53</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.2422462404740058</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19211,12 +19208,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19250,13 +19247,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="O113" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="R113" t="n">
-        <v>0.5887274669818509</v>
+        <v>1.002368047230069</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -19265,7 +19262,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -19290,7 +19287,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -19303,42 +19300,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19370,12 +19367,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19409,29 +19406,29 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="O114" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>VTEC/STEC infection</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -19441,7 +19438,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -19456,7 +19453,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -19491,17 +19488,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -19524,7 +19521,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -19537,42 +19534,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19604,12 +19601,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19634,7 +19631,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19643,81 +19640,95 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="O115" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03430595311776218</v>
+        <v>0.5887274669818509</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19744,17 +19755,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19779,7 +19790,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -19788,81 +19799,170 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="O116" t="n">
-        <v>207</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.05930628934832628</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19924,7 +20024,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -19933,13 +20033,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="O117" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="R117" t="n">
-        <v>0.06697828942039284</v>
+        <v>0.03430595311776218</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20069,7 +20169,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20078,13 +20178,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="O118" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="R118" t="n">
-        <v>0.06045230460143403</v>
+        <v>0.05930628934832628</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20214,7 +20314,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -20223,13 +20323,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="O119" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="R119" t="n">
-        <v>0.07923041553387933</v>
+        <v>0.06697828942039284</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20359,7 +20459,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -20368,13 +20468,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="O120" t="n">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="R120" t="n">
-        <v>0.04870564825707954</v>
+        <v>0.06045230460143403</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20504,7 +20604,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20513,13 +20613,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="O121" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="R121" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.07923041553387933</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20649,7 +20749,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -20764,12 +20864,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20794,22 +20894,22 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="O123" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="R123" t="n">
-        <v>0.2607696391859051</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -20842,42 +20942,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20909,12 +21009,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20939,22 +21039,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>243</v>
+        <v>170</v>
       </c>
       <c r="O124" t="n">
-        <v>243</v>
+        <v>170</v>
       </c>
       <c r="R124" t="n">
-        <v>2.697662625205405</v>
+        <v>0.04870564825707954</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20987,42 +21087,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21054,12 +21154,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21093,95 +21193,81 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="O125" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="R125" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.2607696391859051</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21208,17 +21294,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21252,170 +21338,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="O126" t="n">
-        <v>34</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
+        <v>243</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2.697662625205405</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21447,12 +21444,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21486,81 +21483,95 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="O127" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="R127" t="n">
-        <v>0.2751917291784705</v>
+        <v>0.6047951180938068</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21587,17 +21598,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21631,22 +21642,39 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="O128" t="n">
-        <v>125</v>
-      </c>
-      <c r="R128" t="n">
-        <v>1.168110053535418</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>34</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -21654,6 +21682,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21666,12 +21752,12 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -21679,47 +21765,47 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21746,17 +21832,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21790,170 +21876,81 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="O129" t="n">
-        <v>125</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
+        <v>142</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2751917291784705</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21985,12 +21982,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22015,7 +22012,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22024,81 +22021,95 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O130" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R130" t="n">
-        <v>0.1004674341305892</v>
+        <v>1.168110053535418</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22125,17 +22136,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22160,7 +22171,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22169,81 +22180,170 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="O131" t="n">
-        <v>168</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.04813264063052567</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22405,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22314,13 +22414,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="O132" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="R132" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22450,7 +22550,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22459,13 +22559,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="O133" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="R133" t="n">
-        <v>0.06159831985454178</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22595,7 +22695,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22604,13 +22704,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O134" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="R134" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22740,7 +22840,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -22749,13 +22849,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="O135" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="R135" t="n">
-        <v>0.08222659441048136</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22885,7 +22985,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -22894,13 +22994,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="O136" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23030,7 +23130,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23039,13 +23139,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O137" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="R137" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23175,7 +23275,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23184,13 +23284,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="O138" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="R138" t="n">
-        <v>0.08821530801710276</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23290,12 +23390,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23320,22 +23420,22 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>6</v>
+        <v>297</v>
       </c>
       <c r="O139" t="n">
-        <v>6</v>
+        <v>297</v>
       </c>
       <c r="R139" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23368,42 +23468,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23435,12 +23535,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23465,104 +23565,90 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="O140" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="R140" t="n">
-        <v>0.284609467338262</v>
+        <v>0.08821530801710276</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23589,17 +23675,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23633,170 +23719,81 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O141" t="n">
-        <v>16</v>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.04040093001471769</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT141" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV141" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23828,12 +23825,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23867,81 +23864,95 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O142" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R142" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23968,17 +23979,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24012,81 +24023,170 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="O143" t="n">
-        <v>288</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0.0825130982237583</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24118,12 +24218,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24148,7 +24248,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24157,13 +24257,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="O144" t="n">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="R144" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24196,42 +24296,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24393,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24302,13 +24402,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="O145" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="R145" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24375,6 +24475,296 @@
         </is>
       </c>
       <c r="BC145" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>148</v>
+      </c>
+      <c r="O146" t="n">
+        <v>148</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.1208876443197334</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>310</v>
+      </c>
+      <c r="O147" t="n">
+        <v>310</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.08881618211585095</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24496,7 +24886,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -24506,7 +24896,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -24526,7 +24916,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -24558,7 +24948,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9863</v>
+        <v>9893</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -19102,13 +19102,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O112" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R112" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2441842103977978</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -24257,13 +24257,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O144" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R144" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24767,6 +24767,151 @@
       <c r="BC147" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>143</v>
+      </c>
+      <c r="O148" t="n">
+        <v>143</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.1168036022819046</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24803,7 +24948,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24886,7 +25031,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -24896,7 +25041,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -24948,7 +25093,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9893</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O142" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R142" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24023,10 +24023,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O143" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10041</v>
+        <v>10043</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -23719,13 +23719,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O141" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R141" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.07345623639039579</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R142" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24023,10 +24023,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -24912,6 +24912,151 @@
       <c r="BC148" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>279</v>
+      </c>
+      <c r="O149" t="n">
+        <v>279</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.07993456390426584</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24948,7 +25093,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25176,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -25041,7 +25186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -25093,7 +25238,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10043</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -17884,13 +17884,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O105" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R105" t="n">
-        <v>0.2901521337420634</v>
+        <v>0.2938249455615832</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -21193,13 +21193,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O125" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R125" t="n">
-        <v>0.2607696391859051</v>
+        <v>0.2644424510054249</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R142" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24023,10 +24023,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10332</v>
+        <v>10335</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -23719,13 +23719,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O141" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R141" t="n">
-        <v>0.07345623639039579</v>
+        <v>0.07712904820991559</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R142" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24023,10 +24023,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10335</v>
+        <v>10337</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -23719,13 +23719,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O141" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R141" t="n">
-        <v>0.07712904820991559</v>
+        <v>0.08447467184895517</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10337</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -19102,13 +19102,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O112" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R112" t="n">
-        <v>0.2441842103977978</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -21876,13 +21876,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O129" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R129" t="n">
-        <v>0.2751917291784705</v>
+        <v>0.2790676690260546</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21982,12 +21982,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22021,13 +22021,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="O130" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="R130" t="n">
-        <v>1.168110053535418</v>
+        <v>1.210406698541971</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22074,42 +22074,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22141,12 +22141,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22180,29 +22180,29 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="O131" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>VTEC/STEC infection</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -22262,17 +22262,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -22308,42 +22308,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22375,12 +22375,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22414,81 +22414,95 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O132" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R132" t="n">
-        <v>0.1004674341305892</v>
+        <v>1.168110053535418</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22515,17 +22529,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22550,7 +22564,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22559,81 +22573,170 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="O133" t="n">
-        <v>168</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.04813264063052567</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22695,7 +22798,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22704,13 +22807,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="O134" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="R134" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22840,7 +22943,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -22849,13 +22952,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="O135" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="R135" t="n">
-        <v>0.06159831985454178</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22985,7 +23088,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -22994,13 +23097,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O136" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23130,7 +23233,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23139,13 +23242,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="O137" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="R137" t="n">
-        <v>0.08222659441048136</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23275,7 +23378,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23284,13 +23387,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="O138" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="R138" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23420,7 +23523,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23429,13 +23532,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O139" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="R139" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23565,7 +23668,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23574,13 +23677,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="O140" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="R140" t="n">
-        <v>0.08821530801710276</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23680,12 +23783,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23710,22 +23813,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="O141" t="n">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="R141" t="n">
-        <v>0.08447467184895517</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23758,42 +23861,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23825,12 +23928,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23855,104 +23958,90 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="O142" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="R142" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.08821530801710276</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23979,17 +24068,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24023,170 +24112,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O143" t="n">
-        <v>21</v>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.09182029548799475</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV143" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24218,12 +24218,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24257,81 +24257,95 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="O144" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="R144" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24358,17 +24372,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24402,81 +24416,170 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="O145" t="n">
-        <v>288</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.0825130982237583</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24508,12 +24611,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24538,7 +24641,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -24547,13 +24650,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="O146" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.06007706763755342</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24586,42 +24689,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24786,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24692,13 +24795,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="O147" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="R147" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24828,7 +24931,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24837,13 +24940,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O148" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -24973,7 +25076,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -24982,13 +25085,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="O149" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="R149" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25057,6 +25160,441 @@
       <c r="BC149" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>143</v>
+      </c>
+      <c r="O150" t="n">
+        <v>143</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.1168036022819046</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>279</v>
+      </c>
+      <c r="O151" t="n">
+        <v>279</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.07993456390426584</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>178</v>
+      </c>
+      <c r="O152" t="n">
+        <v>178</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.1453918965467064</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25093,7 +25631,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25714,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -25186,7 +25724,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -25206,7 +25744,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -25238,7 +25776,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10339</v>
+        <v>10620</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -21193,13 +21193,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O125" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R125" t="n">
-        <v>0.2644424510054249</v>
+        <v>0.2681152628249447</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21876,13 +21876,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O129" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R129" t="n">
-        <v>0.2790676690260546</v>
+        <v>0.2810056389498466</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -24112,13 +24112,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O143" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R143" t="n">
-        <v>0.09182029548799475</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10620</v>
+        <v>10623</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -24257,13 +24257,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O144" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R144" t="n">
-        <v>0.7293117600542963</v>
+        <v>0.8004641268888618</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24416,10 +24416,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O145" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -25595,6 +25595,151 @@
       <c r="BC152" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>249</v>
+      </c>
+      <c r="O153" t="n">
+        <v>249</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.07133944950595769</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25776,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -25714,7 +25859,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -25724,7 +25869,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -25776,7 +25921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10623</v>
+        <v>10876</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -19102,13 +19102,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O112" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R112" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -21837,12 +21837,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21876,13 +21876,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0.2810056389498466</v>
+        <v>0</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21915,42 +21915,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21982,12 +21982,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22021,95 +22021,81 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="O130" t="n">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="R130" t="n">
-        <v>1.210406698541971</v>
+        <v>0.2829436088736387</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22136,7 +22122,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -22185,98 +22171,23 @@
       <c r="O131" t="n">
         <v>64</v>
       </c>
+      <c r="R131" t="n">
+        <v>1.210406698541971</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -22370,17 +22281,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22414,22 +22325,39 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="O132" t="n">
-        <v>125</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1.168110053535418</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>64</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>VTEC/STEC infection</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -22437,6 +22365,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22454,7 +22440,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -22467,42 +22453,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22529,7 +22515,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -22578,98 +22564,23 @@
       <c r="O133" t="n">
         <v>125</v>
       </c>
+      <c r="R133" t="n">
+        <v>1.168110053535418</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -22763,17 +22674,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22798,7 +22709,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22807,81 +22718,170 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O134" t="n">
-        <v>123</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0.1004674341305892</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22913,12 +22913,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22952,13 +22952,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="O135" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="R135" t="n">
-        <v>0.04813264063052567</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22991,42 +22991,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23058,12 +23058,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23097,13 +23097,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="O136" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="R136" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23136,42 +23136,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23203,12 +23203,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23242,13 +23242,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>215</v>
+        <v>99</v>
       </c>
       <c r="O137" t="n">
-        <v>215</v>
+        <v>99</v>
       </c>
       <c r="R137" t="n">
-        <v>0.06159831985454178</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23281,42 +23281,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23348,12 +23348,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="O138" t="n">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="R138" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23426,42 +23426,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23493,12 +23493,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23532,13 +23532,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="O139" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="R139" t="n">
-        <v>0.08222659441048136</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23571,42 +23571,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23638,12 +23638,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23677,13 +23677,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="O140" t="n">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="R140" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23716,42 +23716,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23783,12 +23783,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23822,13 +23822,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="O141" t="n">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="R141" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23861,42 +23861,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23928,12 +23928,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -23967,13 +23967,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>108</v>
+        <v>297</v>
       </c>
       <c r="O142" t="n">
-        <v>108</v>
+        <v>297</v>
       </c>
       <c r="R142" t="n">
-        <v>0.08821530801710276</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24006,42 +24006,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24073,12 +24073,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24103,22 +24103,22 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="O143" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="R143" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.08821530801710276</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24151,42 +24151,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24218,12 +24218,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24257,95 +24257,81 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="O144" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="R144" t="n">
-        <v>0.8004641268888618</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24372,7 +24358,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24421,98 +24407,23 @@
       <c r="O145" t="n">
         <v>45</v>
       </c>
+      <c r="R145" t="n">
+        <v>0.8004641268888618</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -24606,17 +24517,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24650,81 +24561,170 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="O146" t="n">
-        <v>31</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.06007706763755342</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24795,13 +24795,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>288</v>
+        <v>36</v>
       </c>
       <c r="O147" t="n">
-        <v>288</v>
+        <v>36</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0825130982237583</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24834,42 +24834,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24901,12 +24901,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24940,13 +24940,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="O148" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -24979,42 +24979,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25046,12 +25046,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25076,7 +25076,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="O149" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="R149" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25124,42 +25124,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25230,13 +25230,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="O150" t="n">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25269,42 +25269,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25336,12 +25336,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25375,13 +25375,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="O151" t="n">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="R151" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25414,42 +25414,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25520,13 +25520,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="O152" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25559,42 +25559,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25626,12 +25626,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -25665,13 +25665,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="O153" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="R153" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25704,40 +25704,185 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>249</v>
+      </c>
+      <c r="O154" t="n">
+        <v>249</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.07133944950595769</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW153" t="inlineStr">
+      <c r="AW154" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX153" t="inlineStr">
+      <c r="AX154" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr">
+      <c r="AY154" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ153" t="inlineStr">
+      <c r="AZ154" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA153" t="inlineStr">
+      <c r="BA154" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB153" t="inlineStr">
+      <c r="BB154" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC153" t="inlineStr">
+      <c r="BC154" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -25859,7 +26004,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -25869,7 +26014,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -25921,7 +26066,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10876</v>
+        <v>10881</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2552,7 +2562,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2560,17 +2570,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2786,7 +2801,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2794,17 +2809,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4960,7 +4980,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -4968,17 +4988,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5194,7 +5219,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5202,17 +5227,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6039,7 +6069,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6047,17 +6077,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6273,7 +6308,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6281,17 +6316,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -8299,7 +8339,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8307,17 +8347,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -8533,7 +8578,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -8541,17 +8586,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9378,7 +9428,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9386,17 +9436,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -9612,7 +9667,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -9620,17 +9675,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11635,7 +11695,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -11643,17 +11703,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -11869,7 +11934,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -11877,17 +11942,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -12711,7 +12781,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -12719,17 +12789,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -12945,7 +13020,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -12953,17 +13028,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14968,7 +15048,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -14976,17 +15056,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -15202,7 +15287,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -15210,17 +15295,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -16044,7 +16134,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -16052,17 +16142,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -16278,7 +16373,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -16286,17 +16381,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18594,7 +18694,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -18602,17 +18702,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -18828,7 +18933,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -18836,17 +18941,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -19670,7 +19780,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -19678,17 +19788,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -19904,7 +20019,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -19912,17 +20027,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -21513,7 +21633,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
@@ -21521,17 +21641,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS127" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -21747,7 +21872,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -21755,17 +21880,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -22589,7 +22719,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -22597,17 +22727,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -22823,7 +22958,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -22831,17 +22966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -24432,7 +24572,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -24440,17 +24580,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS145" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -24666,7 +24811,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -24674,17 +24819,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS146" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -18090,12 +18090,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18129,67 +18129,53 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -18199,17 +18185,17 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
@@ -18241,17 +18227,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18285,145 +18271,53 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O107" t="n">
-        <v>25</v>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Verotoxin Producing E. Coli Including HUS</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary culture-confirmed verotoxin-producing Escherichia coli infection notifications. Although the source title mentions HUS, probable HUS-only, toxin-only and NAAT-only cases are excluded from July 2026 IDTO totals.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV107" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -18433,17 +18327,17 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
@@ -18480,12 +18374,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18519,17 +18413,14 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>164</v>
+        <v>9</v>
       </c>
       <c r="O108" t="n">
-        <v>164</v>
-      </c>
-      <c r="R108" t="n">
-        <v>1.820644734706529</v>
+        <v>9</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -18558,42 +18449,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18625,12 +18516,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18664,100 +18555,78 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O109" t="n">
-        <v>24</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.426914201007393</v>
+        <v>20</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18784,17 +18653,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18828,175 +18697,78 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O110" t="n">
-        <v>24</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT110" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19028,12 +18800,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19067,17 +18839,14 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O111" t="n">
-        <v>2</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.02710540560393419</v>
+        <v>17</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -19106,42 +18875,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19173,12 +18942,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19212,81 +18981,92 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="O112" t="n">
-        <v>124</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0.2403082705502137</v>
+        <v>25</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19313,17 +19093,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19357,22 +19137,39 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="O113" t="n">
-        <v>53</v>
-      </c>
-      <c r="R113" t="n">
-        <v>1.002368047230069</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Verotoxin Producing E. Coli Including HUS</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -19380,6 +19177,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary culture-confirmed verotoxin-producing Escherichia coli infection notifications. Although the source title mentions HUS, probable HUS-only, toxin-only and NAAT-only cases are excluded from July 2026 IDTO totals.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -19397,7 +19252,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -19410,42 +19265,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19472,17 +19327,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19516,170 +19371,81 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="O114" t="n">
-        <v>53</v>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.820644734706529</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -19711,12 +19477,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19750,13 +19516,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="O115" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="R115" t="n">
-        <v>0.5887274669818509</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -19765,7 +19531,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -19785,7 +19551,7 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
@@ -19795,7 +19561,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -19803,47 +19569,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19875,12 +19641,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19914,29 +19680,29 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="O116" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>EHEC</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -19961,7 +19727,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -19996,17 +19762,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20024,7 +19790,7 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
@@ -20034,7 +19800,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20042,47 +19808,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20114,12 +19880,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20144,7 +19910,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20153,13 +19919,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="R117" t="n">
-        <v>0.03430595311776218</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20192,42 +19958,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20259,12 +20025,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20289,7 +20055,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20298,13 +20064,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="O118" t="n">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="R118" t="n">
-        <v>0.05930628934832628</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20337,42 +20103,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20404,12 +20170,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20434,7 +20200,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -20443,56 +20209,70 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="O119" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="R119" t="n">
-        <v>0.06697828942039284</v>
+        <v>1.002368047230069</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -20502,17 +20282,17 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
@@ -20544,17 +20324,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20579,7 +20359,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -20588,81 +20368,170 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>211</v>
+        <v>53</v>
       </c>
       <c r="O120" t="n">
-        <v>211</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.06045230460143403</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>53</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>VTEC/STEC infection</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20694,12 +20563,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20724,7 +20593,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20733,81 +20602,100 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="O121" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="R121" t="n">
-        <v>0.07923041553387933</v>
+        <v>0.5887274669818509</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20834,17 +20722,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20869,7 +20757,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -20878,81 +20766,175 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="O122" t="n">
-        <v>170</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.04870564825707954</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21014,7 +20996,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21023,13 +21005,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="O123" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="R123" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.03430595311776218</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21159,7 +21141,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21168,13 +21150,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="O124" t="n">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="R124" t="n">
-        <v>0.04870564825707954</v>
+        <v>0.05930628934832628</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21274,12 +21256,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21304,22 +21286,22 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="O125" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="R125" t="n">
-        <v>0.2681152628249447</v>
+        <v>0.06697828942039284</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21352,42 +21334,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21419,12 +21401,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21449,22 +21431,22 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="O126" t="n">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="R126" t="n">
-        <v>2.697662625205405</v>
+        <v>0.06045230460143403</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -21497,42 +21479,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21564,12 +21546,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21594,109 +21576,90 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="O127" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="R127" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.07923041553387933</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21723,17 +21686,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21758,184 +21721,90 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="O128" t="n">
-        <v>34</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.04870564825707954</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21967,12 +21836,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21997,22 +21866,22 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22045,42 +21914,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22112,12 +21981,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22142,22 +22011,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="O130" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2829436088736387</v>
+        <v>0.04870564825707954</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22190,42 +22059,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22257,12 +22126,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22296,95 +22165,81 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="O131" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="R131" t="n">
-        <v>1.210406698541971</v>
+        <v>0.279133698283504</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22411,17 +22266,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22455,170 +22310,78 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>64</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22650,12 +22413,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22689,100 +22452,78 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="O133" t="n">
-        <v>125</v>
-      </c>
-      <c r="R133" t="n">
-        <v>1.168110053535418</v>
+        <v>10</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22809,17 +22550,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22853,175 +22594,78 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="O134" t="n">
-        <v>125</v>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="AT134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV134" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23053,12 +22697,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23083,7 +22727,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23092,17 +22736,14 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="O135" t="n">
-        <v>123</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0.1004674341305892</v>
+        <v>23</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -23131,42 +22772,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23198,12 +22839,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23228,7 +22869,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23237,17 +22878,14 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="O136" t="n">
-        <v>168</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.04813264063052567</v>
+        <v>18</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -23276,42 +22914,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23343,12 +22981,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23373,7 +23011,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23382,17 +23020,14 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="O137" t="n">
-        <v>99</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.08086403234901086</v>
+        <v>11</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -23421,42 +23056,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23488,12 +23123,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23518,7 +23153,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23527,13 +23162,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="O138" t="n">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="R138" t="n">
-        <v>0.06159831985454178</v>
+        <v>2.697662625205405</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23566,42 +23201,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -23633,12 +23268,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23663,7 +23298,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23672,81 +23307,100 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="O139" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="R139" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.6047951180938068</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23773,17 +23427,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23808,7 +23462,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23817,81 +23471,175 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>287</v>
+        <v>34</v>
       </c>
       <c r="O140" t="n">
-        <v>287</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0.08222659441048136</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23923,12 +23671,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23953,7 +23701,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -23962,13 +23710,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.1029178593532865</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24001,42 +23749,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24068,12 +23816,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24098,7 +23846,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24107,13 +23855,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>297</v>
+        <v>145</v>
       </c>
       <c r="O142" t="n">
-        <v>297</v>
+        <v>145</v>
       </c>
       <c r="R142" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.2810056389498466</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24146,42 +23894,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24213,12 +23961,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24243,7 +23991,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24252,56 +24000,70 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="O143" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="R143" t="n">
-        <v>0.08821530801710276</v>
+        <v>1.210406698541971</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -24311,17 +24073,17 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -24353,17 +24115,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24388,90 +24150,179 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N144" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="O144" t="n">
-        <v>26</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.09549310730751455</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>VTEC/STEC infection</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24503,12 +24354,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24533,22 +24384,22 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="O145" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="R145" t="n">
-        <v>0.8004641268888618</v>
+        <v>1.168110053535418</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24557,7 +24408,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -24577,7 +24428,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -24587,7 +24438,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -24595,47 +24446,47 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24667,12 +24518,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24697,38 +24548,38 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N146" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="O146" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>EHEC</t>
+          <t>Enterohemorragisk E. coli-infektion</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -24753,7 +24604,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -24788,17 +24639,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -24816,7 +24667,7 @@
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
@@ -24826,7 +24677,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -24834,47 +24685,47 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24906,12 +24757,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24936,22 +24787,22 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="O147" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="R147" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24984,42 +24835,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25081,22 +24932,22 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>288</v>
+        <v>168</v>
       </c>
       <c r="O148" t="n">
-        <v>288</v>
+        <v>168</v>
       </c>
       <c r="R148" t="n">
-        <v>0.0825130982237583</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25226,22 +25077,22 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="O149" t="n">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="R149" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25371,22 +25222,22 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="O150" t="n">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="R150" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25516,22 +25367,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="O151" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="R151" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25661,22 +25512,22 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O152" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="R152" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25806,22 +25657,22 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="O153" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25951,22 +25802,22 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="O154" t="n">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="R154" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26035,6 +25886,3694 @@
       <c r="BC154" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>108</v>
+      </c>
+      <c r="O155" t="n">
+        <v>108</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0.08821530801710276</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>31</v>
+      </c>
+      <c r="O156" t="n">
+        <v>31</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.1138571664051135</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>6</v>
+      </c>
+      <c r="O158" t="n">
+        <v>6</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>10</v>
+      </c>
+      <c r="O160" t="n">
+        <v>10</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>10</v>
+      </c>
+      <c r="O162" t="n">
+        <v>10</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>55</v>
+      </c>
+      <c r="O163" t="n">
+        <v>55</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.9783450439752756</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>55</v>
+      </c>
+      <c r="O164" t="n">
+        <v>55</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>43</v>
+      </c>
+      <c r="O165" t="n">
+        <v>43</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.08333270672305797</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>288</v>
+      </c>
+      <c r="O166" t="n">
+        <v>288</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.0825130982237583</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>148</v>
+      </c>
+      <c r="O167" t="n">
+        <v>148</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.1208876443197334</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>310</v>
+      </c>
+      <c r="O168" t="n">
+        <v>310</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.08881618211585095</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>143</v>
+      </c>
+      <c r="O169" t="n">
+        <v>143</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.1168036022819046</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>279</v>
+      </c>
+      <c r="O170" t="n">
+        <v>279</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.07993456390426584</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>178</v>
+      </c>
+      <c r="O171" t="n">
+        <v>178</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.1453918965467064</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>249</v>
+      </c>
+      <c r="O172" t="n">
+        <v>249</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.07133944950595769</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>213</v>
+      </c>
+      <c r="O173" t="n">
+        <v>213</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.1739801908115082</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>250</v>
+      </c>
+      <c r="O174" t="n">
+        <v>250</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.07162595331923463</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26071,7 +29610,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -26154,7 +29693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -26164,7 +29703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -26184,7 +29723,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -26216,7 +29755,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10881</v>
+        <v>11548</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -27098,13 +27098,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O163" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R163" t="n">
-        <v>0.9783450439752756</v>
+        <v>1.013921227392558</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -27262,10 +27262,10 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O164" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O165" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R165" t="n">
-        <v>0.08333270672305797</v>
+        <v>0.0891466164944341</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -29096,13 +29096,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29260,10 +29260,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11548</v>
+        <v>11554</v>
       </c>
     </row>
     <row r="16">
